--- a/DateBase/orders/Nhat 48_2026-3-4.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-4.xlsx
@@ -520,6 +520,9 @@
       <c r="A11" t="str">
         <v>3</v>
       </c>
+      <c r="C11" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nhat 48_2026-3-4.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-4.xlsx
@@ -523,6 +523,9 @@
       <c r="C11" t="str">
         <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -581,7 +584,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0451512445515450</v>
+        <v>04515124455154545</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-4.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -527,9 +527,99 @@
         <v>45</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>4</v>
+      </c>
+      <c r="C12" t="str">
+        <v>820_蝴蝶洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5</v>
+      </c>
+      <c r="C13" t="str">
+        <v>589_洋牡丹香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>6</v>
+      </c>
+      <c r="C16" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>468_水仙百合_Alstroemeria_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>7</v>
+      </c>
+      <c r="C19" t="str">
+        <v>320_雪柳花_Spiraea flower white_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F20" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">509_翠珠粉_Didiscus caeruleus
+pink_Trachymene Coerulea_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -584,7 +674,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>04515124455154545</v>
+        <v>045151244551545458040510610530350</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-4.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-4.xlsx
@@ -616,6 +616,9 @@
         <v xml:space="preserve">509_翠珠粉_Didiscus caeruleus
 pink_Trachymene Coerulea_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -674,7 +677,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>045151244551545458040510610530350</v>
+        <v>045151244551545458040510610530355</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-4.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -620,9 +620,25 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -677,7 +693,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>045151244551545458040510610530355</v>
+        <v>04515124455154545804051061053035558</v>
       </c>
     </row>
   </sheetData>
